--- a/brain_organization.xlsx
+++ b/brain_organization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programação Semanal" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados_SMS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plano System Design" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funil" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Programação Semanal" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dados_SMS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Plano System Design" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Funil" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados_SMS'!$A$1:$E$43</definedName>
@@ -193,7 +193,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -273,11 +273,44 @@
         <color rgb="00B0BEC5"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0BEC5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0BEC5"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0BEC5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0BEC5"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0BEC5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0BEC5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -414,6 +447,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1114,7 +1148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1125,1539 +1159,1658 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Dia</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Dia_EN</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Ativo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Segunda</t>
         </is>
       </c>
-      <c r="B2" s="24" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C2" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D2" s="24" t="inlineStr">
-        <is>
-          <t>06h30 - Open English (20min)</t>
-        </is>
-      </c>
-      <c r="E2" s="24" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Devocional</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Segunda</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D3" s="24" t="inlineStr">
-        <is>
-          <t>17h00 - 1 Notícia (10min)</t>
-        </is>
-      </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Palavra</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Segunda</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>17h40 - Conversa IA (15min)</t>
-        </is>
-      </c>
-      <c r="E4" s="24" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Leitura em inglês (40 min)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Segunda</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Tech</t>
-        </is>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
-        <is>
-          <t>06h50 - DSA: 1 problema (20min)</t>
-        </is>
-      </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Caça de aplicações (40 min)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Segunda</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Tech</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
-        <is>
-          <t>07h10 - System Design 1h (ver Plano SD)</t>
-        </is>
-      </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LeetCode (1 hora)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Segunda</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Tech</t>
-        </is>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
-        <is>
-          <t>08h10 - Python (20min)</t>
-        </is>
-      </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>System Designer (40 min)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Segunda</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Tech</t>
-        </is>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
-        <is>
-          <t>17h10 - Revisão (30min)</t>
-        </is>
-      </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Atividades open english (25 min)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Segunda</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>Aplicações</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
-        <is>
-          <t>17h55 - 5 aplicações LinkedIn/Wellfound (30min)</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bible is Open (1 hora)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Segunda</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Bíblicos</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>23h30 - Escatologia (30min)</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mock interview IA (25 min)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="inlineStr">
-        <is>
-          <t>06h30 - Open English (20min)</t>
-        </is>
-      </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Devocional</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="inlineStr">
-        <is>
-          <t>17h00 - Aula online (40min)</t>
-        </is>
-      </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Palavra</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="inlineStr">
-        <is>
-          <t>17h40 - Conversa IA (15min)</t>
-        </is>
-      </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Aula de Inglês online (40 min)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Tech</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>06h50 - DSA: 1 problema (20min)</t>
-        </is>
-      </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Caça de aplicações (40 min)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Tech</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>07h10 - System Design 1h (ver Plano SD)</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LeetCode (1 hora)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>Aplicações</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>17h55 - 5 aplicações LinkedIn/Wellfound (30min)</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>System Designer (40 min)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Bíblicos</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>23h30 - História da Igreja (30min)</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Atividades open english (25 min)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bible is Open (1 hora)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mock interview IA (25 min)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Quarta</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>06h30 - Open English (20min)</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Devocional</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Quarta</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>17h00 - 1 Notícia (10min)</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Palavra</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Quarta</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>17h40 - Conversa IA (15min)</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Leitura em inglês (40 min)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Quarta</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Tech</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>06h50 - DSA: 1 problema (20min)</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Caça de aplicações (40 min)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Quarta</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Tech</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>07h10 - System Design 1h (ver Plano SD)</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LeetCode (1 hora)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Quarta</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Tech</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
-        <is>
-          <t>08h10 - Python (20min)</t>
-        </is>
-      </c>
-      <c r="E23" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>System Designer (40 min)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Quarta</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Tech</t>
-        </is>
-      </c>
-      <c r="D24" s="24" t="inlineStr">
-        <is>
-          <t>17h10 - Revisão (30min)</t>
-        </is>
-      </c>
-      <c r="E24" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Atividades open english (25 min)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Quarta</t>
         </is>
       </c>
-      <c r="B25" s="24" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
-        <is>
-          <t>Aplicações</t>
-        </is>
-      </c>
-      <c r="D25" s="24" t="inlineStr">
-        <is>
-          <t>17h55 - 5 aplicações LinkedIn/Wellfound (30min)</t>
-        </is>
-      </c>
-      <c r="E25" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bible is Open (1 hora)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Quarta</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Bíblicos</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr">
-        <is>
-          <t>23h30 - Escatologia (30min)</t>
-        </is>
-      </c>
-      <c r="E26" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Mock interview IA (25 min)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Quinta</t>
         </is>
       </c>
-      <c r="B27" s="24" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D27" s="24" t="inlineStr">
-        <is>
-          <t>06h30 - Open English (20min)</t>
-        </is>
-      </c>
-      <c r="E27" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Devocional</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Quinta</t>
         </is>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D28" s="24" t="inlineStr">
-        <is>
-          <t>17h00 - Aula online (40min)</t>
-        </is>
-      </c>
-      <c r="E28" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Palavra</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Quinta</t>
         </is>
       </c>
-      <c r="B29" s="24" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D29" s="24" t="inlineStr">
-        <is>
-          <t>17h40 - Conversa IA (15min)</t>
-        </is>
-      </c>
-      <c r="E29" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Aula de inglês particular online (40 min)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Quinta</t>
         </is>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Tech</t>
-        </is>
-      </c>
-      <c r="D30" s="24" t="inlineStr">
-        <is>
-          <t>06h50 - DSA: 1 problema (20min)</t>
-        </is>
-      </c>
-      <c r="E30" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Caça de aplicações (40 min)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Quinta</t>
         </is>
       </c>
-      <c r="B31" s="24" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C31" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Tech</t>
-        </is>
-      </c>
-      <c r="D31" s="24" t="inlineStr">
-        <is>
-          <t>07h10 - System Design 1h (ver Plano SD)</t>
-        </is>
-      </c>
-      <c r="E31" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LeetCode (1 hora)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Quinta</t>
         </is>
       </c>
-      <c r="B32" s="24" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
-        <is>
-          <t>Aplicações</t>
-        </is>
-      </c>
-      <c r="D32" s="24" t="inlineStr">
-        <is>
-          <t>17h55 - 5 aplicações LinkedIn/Wellfound (30min)</t>
-        </is>
-      </c>
-      <c r="E32" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="24" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>System Designer (40 min)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Quinta</t>
         </is>
       </c>
-      <c r="B33" s="24" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Bíblicos</t>
-        </is>
-      </c>
-      <c r="D33" s="24" t="inlineStr">
-        <is>
-          <t>23h30 - História da Igreja (30min)</t>
-        </is>
-      </c>
-      <c r="E33" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Atividades open english (25 min)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Quinta</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Bible is Open (1 hora)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Quinta</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Mock interview IA (25 min)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D34" s="24" t="inlineStr">
-        <is>
-          <t>06h30 - Open English (20min)</t>
-        </is>
-      </c>
-      <c r="E34" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="24" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Devocional</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="B35" s="24" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D35" s="24" t="inlineStr">
-        <is>
-          <t>17h00 - Aula online (40min)</t>
-        </is>
-      </c>
-      <c r="E35" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="24" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Palavra</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="B36" s="24" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D36" s="24" t="inlineStr">
-        <is>
-          <t>17h40 - 1 Notícia (10min)</t>
-        </is>
-      </c>
-      <c r="E36" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="24" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Vídeo em inglês (40 min)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="B37" s="24" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D37" s="24" t="inlineStr">
-        <is>
-          <t>17h50 - Conversa IA (15min)</t>
-        </is>
-      </c>
-      <c r="E37" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="24" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Caça de aplicações (40 min)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="B38" s="24" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Tech</t>
-        </is>
-      </c>
-      <c r="D38" s="24" t="inlineStr">
-        <is>
-          <t>06h50 - DSA: 1 problema (20min)</t>
-        </is>
-      </c>
-      <c r="E38" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="24" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LeetCode (1 hora)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="B39" s="24" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C39" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Tech</t>
-        </is>
-      </c>
-      <c r="D39" s="24" t="inlineStr">
-        <is>
-          <t>07h10 - System Design 1h (ver Plano SD)</t>
-        </is>
-      </c>
-      <c r="E39" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="24" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>System Designer (40 min)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="B40" s="24" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Tech</t>
-        </is>
-      </c>
-      <c r="D40" s="24" t="inlineStr">
-        <is>
-          <t>08h10 - Python (20min)</t>
-        </is>
-      </c>
-      <c r="E40" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="24" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Atividades open english (25 min)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="B41" s="24" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C41" s="24" t="inlineStr">
-        <is>
-          <t>Aplicações</t>
-        </is>
-      </c>
-      <c r="D41" s="24" t="inlineStr">
-        <is>
-          <t>18h05 - 5 aplicações LinkedIn/Wellfound (30min)</t>
-        </is>
-      </c>
-      <c r="E41" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Bible is Open (1 hora)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="B42" s="24" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C42" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Bíblicos</t>
-        </is>
-      </c>
-      <c r="D42" s="24" t="inlineStr">
-        <is>
-          <t>23h30 - Escatologia (30min)</t>
-        </is>
-      </c>
-      <c r="E42" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="24" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Mock interview IA (25 min)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Sábado</t>
         </is>
       </c>
-      <c r="B43" s="24" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C43" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D43" s="24" t="inlineStr">
-        <is>
-          <t>Open English (20min)</t>
-        </is>
-      </c>
-      <c r="E43" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="24" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Devocional</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Sábado</t>
         </is>
       </c>
-      <c r="B44" s="24" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C44" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D44" s="24" t="inlineStr">
-        <is>
-          <t>1 Notícia (10min)</t>
-        </is>
-      </c>
-      <c r="E44" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="24" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Palavra</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Sábado</t>
         </is>
       </c>
-      <c r="B45" s="24" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C45" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D45" s="24" t="inlineStr">
-        <is>
-          <t>Vídeo tech em inglês (20min)</t>
-        </is>
-      </c>
-      <c r="E45" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="24" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Aula de Inglês online (40 min)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Sábado</t>
         </is>
       </c>
-      <c r="B46" s="24" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C46" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D46" s="24" t="inlineStr">
-        <is>
-          <t>Conversa IA (15min)</t>
-        </is>
-      </c>
-      <c r="E46" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="24" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Caça de aplicações (40 min)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Sábado</t>
         </is>
       </c>
-      <c r="B47" s="24" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C47" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Tech</t>
-        </is>
-      </c>
-      <c r="D47" s="24" t="inlineStr">
-        <is>
-          <t>Revisão (30min)</t>
-        </is>
-      </c>
-      <c r="E47" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="24" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LeetCode (1 hora)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Sábado</t>
         </is>
       </c>
-      <c r="B48" s="24" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C48" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Tech</t>
-        </is>
-      </c>
-      <c r="D48" s="24" t="inlineStr">
-        <is>
-          <t>Python (30min)</t>
-        </is>
-      </c>
-      <c r="E48" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="24" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>System Designer (40 min)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Sábado</t>
         </is>
       </c>
-      <c r="B49" s="24" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C49" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Tech</t>
-        </is>
-      </c>
-      <c r="D49" s="24" t="inlineStr">
-        <is>
-          <t>DSA sessão longa (45min)</t>
-        </is>
-      </c>
-      <c r="E49" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="24" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Atividades open english (25 min)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Sábado</t>
         </is>
       </c>
-      <c r="B50" s="24" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C50" s="24" t="inlineStr">
-        <is>
-          <t>Aplicações</t>
-        </is>
-      </c>
-      <c r="D50" s="24" t="inlineStr">
-        <is>
-          <t>Outreach: 5 mensagens p/ recruiters (30min)</t>
-        </is>
-      </c>
-      <c r="E50" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="24" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Bible is Open (1 hora)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Sábado</t>
         </is>
       </c>
-      <c r="B51" s="24" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C51" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Bíblicos</t>
-        </is>
-      </c>
-      <c r="D51" s="24" t="inlineStr">
-        <is>
-          <t>23h30 - História da Igreja (30min)</t>
-        </is>
-      </c>
-      <c r="E51" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="24" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Mock interview IA (25 min)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Domingo</t>
         </is>
       </c>
-      <c r="B52" s="24" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C52" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D52" s="24" t="inlineStr">
-        <is>
-          <t>Revisão (20min)</t>
-        </is>
-      </c>
-      <c r="E52" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="24" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Devocional</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Domingo</t>
         </is>
       </c>
-      <c r="B53" s="24" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C53" s="24" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="D53" s="24" t="inlineStr">
-        <is>
-          <t>Conversa IA (15min)</t>
-        </is>
-      </c>
-      <c r="E53" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="24" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Palavra</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Domingo</t>
         </is>
       </c>
-      <c r="B54" s="24" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C54" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Tech</t>
-        </is>
-      </c>
-      <c r="D54" s="24" t="inlineStr">
-        <is>
-          <t>Revisão (30min)</t>
-        </is>
-      </c>
-      <c r="E54" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="24" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Vídeo em inglês (40 min)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Domingo</t>
         </is>
       </c>
-      <c r="B55" s="24" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C55" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Tech</t>
-        </is>
-      </c>
-      <c r="D55" s="24" t="inlineStr">
-        <is>
-          <t>Planejar semana (15min)</t>
-        </is>
-      </c>
-      <c r="E55" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="24" t="inlineStr">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Caça de aplicações (40 min)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Domingo</t>
         </is>
       </c>
-      <c r="B56" s="24" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C56" s="24" t="inlineStr">
-        <is>
-          <t>Aplicações</t>
-        </is>
-      </c>
-      <c r="D56" s="24" t="inlineStr">
-        <is>
-          <t>Revisar funil da semana (10min)</t>
-        </is>
-      </c>
-      <c r="E56" s="24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="24" t="inlineStr">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>The three of the day:</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LeetCode (1 hora)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Domingo</t>
         </is>
       </c>
-      <c r="B57" s="24" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C57" s="24" t="inlineStr">
-        <is>
-          <t>Estudos Bíblicos</t>
-        </is>
-      </c>
-      <c r="D57" s="24" t="inlineStr">
-        <is>
-          <t>23h30 - Revisão (30min)</t>
-        </is>
-      </c>
-      <c r="E57" s="24" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>System Designer (40 min)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Domingo</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Atividades open english (25 min)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Domingo</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Bible is Open (1 hora)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Domingo</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>With the rest of the time:</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Mock interview IA (25 min)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2865,11 +3018,13 @@
           <t>System Design Primer</t>
         </is>
       </c>
+      <c r="B12" s="48" t="n"/>
       <c r="C12" s="23" t="inlineStr">
         <is>
           <t>PDF que geramos (ou github.com/donnemartin/system-design-primer)</t>
         </is>
       </c>
+      <c r="D12" s="48" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="43" t="inlineStr">
@@ -2877,11 +3032,13 @@
           <t>ByteByteGo (YouTube)</t>
         </is>
       </c>
+      <c r="B13" s="48" t="n"/>
       <c r="C13" s="23" t="inlineStr">
         <is>
           <t>youtube.com/@ByteByteGo — vídeo do conceito, gratuito</t>
         </is>
       </c>
+      <c r="D13" s="48" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="43" t="inlineStr">
@@ -2889,11 +3046,13 @@
           <t>High Scalability</t>
         </is>
       </c>
+      <c r="B14" s="48" t="n"/>
       <c r="C14" s="23" t="inlineStr">
         <is>
           <t>highscalability.com — arquiteturas reais (Netflix, Discord)</t>
         </is>
       </c>
+      <c r="D14" s="48" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="43" t="inlineStr">
@@ -2901,11 +3060,13 @@
           <t>Anotações do Revanth</t>
         </is>
       </c>
+      <c r="B15" s="48" t="n"/>
       <c r="C15" s="23" t="inlineStr">
         <is>
           <t>PDF que você já tem — revisão rápida antes de mock</t>
         </is>
       </c>
+      <c r="D15" s="48" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="43" t="inlineStr">
@@ -2913,11 +3074,13 @@
           <t>LeetCode</t>
         </is>
       </c>
+      <c r="B16" s="48" t="n"/>
       <c r="C16" s="23" t="inlineStr">
         <is>
           <t>leetcode.com/studyplan/top-interview-150 — DSA diário</t>
         </is>
       </c>
+      <c r="D16" s="48" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="43" t="inlineStr">
@@ -2925,11 +3088,13 @@
           <t>NeetCode</t>
         </is>
       </c>
+      <c r="B17" s="48" t="n"/>
       <c r="C17" s="23" t="inlineStr">
         <is>
           <t>neetcode.io/practice — roadmap visual com vídeos-solução</t>
         </is>
       </c>
+      <c r="D17" s="48" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
